--- a/data/trans_orig/IQ14-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IQ14-Edad-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Número de días que los menores se han tenido que quedar en la cama más de medio día por motivos de salud</t>
+          <t>Número de días que los menores se han tenido que quedar en la cama más de medio día por motivos de salud (tasa de respuesta: 97,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,7 +716,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,96; 5,34</t>
+          <t>1,85; 5,3</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -726,17 +726,17 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,13; 4,67</t>
+          <t>2,02; 4,72</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,15; 6,43</t>
+          <t>2,15; 6,12</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,93; 5,06</t>
+          <t>1,97; 5,33</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -751,12 +751,12 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,66; 9,13</t>
+          <t>1,69; 9,14</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,26; 4,54</t>
+          <t>2,33; 4,59</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,23; 4,22</t>
+          <t>2,14; 4,21</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,51; 7,01</t>
+          <t>2,47; 6,89</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,58; 5,94</t>
+          <t>1,6; 5,53</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,52; 3,97</t>
+          <t>1,56; 3,96</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,95; 4,88</t>
+          <t>1,99; 5,01</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,76; 6,11</t>
+          <t>3,76; 6,07</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,99; 5,72</t>
+          <t>2,07; 5,78</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,53; 3,24</t>
+          <t>1,5; 3,33</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,32; 2,32</t>
+          <t>1,28; 2,26</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,57; 5,0</t>
+          <t>2,57; 5,13</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,0; 4,14</t>
+          <t>2,05; 4,55</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,7; 2,94</t>
+          <t>1,69; 3,03</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,8; 3,41</t>
+          <t>1,78; 3,37</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,39; 5,15</t>
+          <t>3,34; 5,15</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,36; 11,47</t>
+          <t>1,37; 11,47</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,01; 5,8</t>
+          <t>2,01; 5,68</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,29; 4,02</t>
+          <t>1,27; 3,88</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,07; 6,75</t>
+          <t>3,08; 6,91</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,72; 3,13</t>
+          <t>1,72; 3,11</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,15; 3,05</t>
+          <t>1,12; 2,88</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,45; 2,07</t>
+          <t>1,44; 2,07</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,19; 8,11</t>
+          <t>3,07; 7,8</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,93; 5,23</t>
+          <t>1,99; 5,26</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,83; 4,59</t>
+          <t>1,9; 4,36</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,53; 2,8</t>
+          <t>1,53; 2,73</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,4; 6,61</t>
+          <t>3,45; 6,64</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,33; 3,67</t>
+          <t>1,32; 3,61</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,44; 3,64</t>
+          <t>1,37; 3,31</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,92; 8,38</t>
+          <t>1,95; 8,4</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,05; 3,36</t>
+          <t>2,04; 3,35</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,29; 3,7</t>
+          <t>1,29; 3,88</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,78; 6,12</t>
+          <t>1,81; 6,27</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,11; 3,16</t>
+          <t>1,11; 3,13</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,78; 12,1</t>
+          <t>4,83; 11,52</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,45; 3,14</t>
+          <t>1,42; 3,09</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,81; 4,22</t>
+          <t>1,79; 4,28</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,76; 5,36</t>
+          <t>1,76; 4,98</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3,65; 7,6</t>
+          <t>3,59; 7,34</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,08; 4,2</t>
+          <t>2,09; 3,93</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,04; 3,24</t>
+          <t>2,08; 3,32</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,23; 3,78</t>
+          <t>2,27; 3,83</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,2; 4,7</t>
+          <t>3,18; 4,63</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,22; 3,68</t>
+          <t>2,15; 3,5</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,91; 3,3</t>
+          <t>1,92; 3,24</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,58; 2,31</t>
+          <t>1,61; 2,35</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>3,92; 6,65</t>
+          <t>3,99; 6,87</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,27; 3,44</t>
+          <t>2,26; 3,4</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2,13; 3,0</t>
+          <t>2,12; 3,03</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2,03; 2,9</t>
+          <t>2,01; 2,9</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,88; 5,61</t>
+          <t>3,89; 5,5</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ14-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IQ14-Edad-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Número de días que los menores se han tenido que quedar en la cama más de medio día por motivos de salud (tasa de respuesta: 97,77%)</t>
+          <t>Tiempo demio en días que en las últimas 2 semanas los menores se han tenido que quedar en la cama más de medio día por motivos de salud (tasa de respuesta: 97,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,85; 5,3</t>
+          <t>1,86; 5,42</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,87; 4,35</t>
+          <t>1,85; 4,43</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,02; 4,72</t>
+          <t>2,03; 4,55</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,15; 6,12</t>
+          <t>2,24; 6,27</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,97; 5,33</t>
+          <t>2,02; 5,31</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,71; 4,41</t>
+          <t>1,68; 4,39</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,66; 4,99</t>
+          <t>1,83; 4,88</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,69; 9,14</t>
+          <t>1,54; 9,12</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,33; 4,59</t>
+          <t>2,33; 4,77</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,97; 3,76</t>
+          <t>1,98; 3,71</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,14; 4,21</t>
+          <t>2,22; 4,39</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,47; 6,89</t>
+          <t>2,5; 6,75</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,6; 5,53</t>
+          <t>1,57; 5,22</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,56; 3,96</t>
+          <t>1,57; 3,94</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,99; 5,01</t>
+          <t>1,97; 4,69</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,76; 6,07</t>
+          <t>3,81; 6,05</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,07; 5,78</t>
+          <t>2,07; 5,43</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,5; 3,33</t>
+          <t>1,51; 3,15</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,28; 2,26</t>
+          <t>1,3; 2,35</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,57; 5,13</t>
+          <t>2,63; 5,12</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,05; 4,55</t>
+          <t>1,99; 4,27</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,69; 3,03</t>
+          <t>1,66; 2,98</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,78; 3,37</t>
+          <t>1,73; 3,32</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,34; 5,15</t>
+          <t>3,35; 5,17</t>
         </is>
       </c>
     </row>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,01; 5,68</t>
+          <t>2,0; 5,92</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1011,47 +1011,47 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,08; 6,91</t>
+          <t>3,17; 7,47</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,72; 3,11</t>
+          <t>1,68; 3,04</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,12; 2,88</t>
+          <t>1,12; 3,01</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,44; 2,07</t>
+          <t>1,46; 2,07</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,07; 7,8</t>
+          <t>3,12; 7,88</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,99; 5,26</t>
+          <t>1,91; 4,95</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,9; 4,36</t>
+          <t>1,79; 4,19</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,53; 2,73</t>
+          <t>1,53; 2,79</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,45; 6,64</t>
+          <t>3,45; 6,78</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,32; 3,61</t>
+          <t>1,38; 3,71</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,37; 3,31</t>
+          <t>1,33; 3,32</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,95; 8,4</t>
+          <t>2,0; 8,27</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,04; 3,35</t>
+          <t>2,03; 3,36</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,29; 3,88</t>
+          <t>1,25; 3,79</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,81; 6,27</t>
+          <t>1,9; 6,4</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,11; 3,13</t>
+          <t>1,19; 3,31</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,83; 11,52</t>
+          <t>4,69; 11,59</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,42; 3,09</t>
+          <t>1,49; 3,15</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,79; 4,28</t>
+          <t>1,85; 4,4</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,76; 4,98</t>
+          <t>1,76; 4,75</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3,59; 7,34</t>
+          <t>3,5; 7,86</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,09; 3,93</t>
+          <t>2,03; 3,92</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,08; 3,32</t>
+          <t>2,03; 3,23</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,27; 3,83</t>
+          <t>2,26; 3,87</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,18; 4,63</t>
+          <t>3,25; 4,72</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,15; 3,5</t>
+          <t>2,14; 3,6</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,92; 3,24</t>
+          <t>1,94; 3,29</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,61; 2,35</t>
+          <t>1,62; 2,28</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>3,99; 6,87</t>
+          <t>3,97; 6,69</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,26; 3,4</t>
+          <t>2,27; 3,39</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2,12; 3,03</t>
+          <t>2,12; 3,0</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2,01; 2,9</t>
+          <t>2,04; 2,98</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,89; 5,5</t>
+          <t>3,88; 5,51</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ14-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IQ14-Edad-trans_orig.xlsx
@@ -526,13 +526,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Tiempo demio en días que en las últimas 2 semanas los menores se han tenido que quedar en la cama más de medio día por motivos de salud (tasa de respuesta: 97,77%)</t>
+          <t>Tiempo medio en días que en las últimas 2 semanas los menores se han tenido que quedar en la cama más de medio día por motivos de salud (tasa de respuesta: 97,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -540,7 +540,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -648,44 +648,44 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>3,19</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2,43</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2,79</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>4,52</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>3,32</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>2,83</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>3,15</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>3,66</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>3,19</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>2,43</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>2,79</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>4,75</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
           <t>3,25</t>
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>4,15</t>
+          <t>4,05</t>
         </is>
       </c>
     </row>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,86; 5,42</t>
+          <t>1,93; 5,06</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,85; 4,43</t>
+          <t>1,71; 4,41</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,03; 4,55</t>
+          <t>1,66; 4,99</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,24; 6,27</t>
+          <t>1,48; 9,09</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,02; 5,31</t>
+          <t>1,96; 5,34</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,68; 4,39</t>
+          <t>1,87; 4,35</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,83; 4,88</t>
+          <t>2,13; 4,67</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,54; 9,12</t>
+          <t>2,15; 6,58</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,33; 4,77</t>
+          <t>2,26; 4,54</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,98; 3,71</t>
+          <t>1,97; 3,76</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,22; 4,39</t>
+          <t>2,23; 4,22</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,5; 6,75</t>
+          <t>2,43; 6,86</t>
         </is>
       </c>
     </row>
@@ -788,42 +788,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>3,13</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>2,07</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1,68</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>3,6</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>2,4</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>2,4</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>2,78</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>5,08</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>3,13</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>2,07</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>1,68</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>3,64</t>
+          <t>5,11</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>4,19</t>
+          <t>4,22</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,57; 5,22</t>
+          <t>1,99; 5,72</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,57; 3,94</t>
+          <t>1,53; 3,24</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,97; 4,69</t>
+          <t>1,32; 2,32</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,81; 6,05</t>
+          <t>2,48; 5,1</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,07; 5,43</t>
+          <t>1,58; 5,94</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,51; 3,15</t>
+          <t>1,52; 3,97</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,3; 2,35</t>
+          <t>1,95; 4,88</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,63; 5,12</t>
+          <t>3,66; 6,2</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,99; 4,27</t>
+          <t>2,0; 4,14</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,66; 2,98</t>
+          <t>1,7; 2,94</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,73; 3,32</t>
+          <t>1,8; 3,41</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,35; 5,17</t>
+          <t>3,35; 5,28</t>
         </is>
       </c>
     </row>
@@ -928,42 +928,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>2,31</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1,89</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1,78</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>4,77</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>4,12</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>3,21</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>2,0</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>4,49</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>2,31</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>1,89</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>1,78</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>4,68</t>
+          <t>4,53</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>4,6</t>
+          <t>4,67</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,37; 11,47</t>
+          <t>1,72; 3,13</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,0; 5,92</t>
+          <t>1,15; 3,05</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,27; 3,88</t>
+          <t>1,45; 2,07</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,17; 7,47</t>
+          <t>3,21; 8,25</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,68; 3,04</t>
+          <t>1,36; 11,47</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,12; 3,01</t>
+          <t>2,01; 5,8</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,46; 2,07</t>
+          <t>1,29; 4,02</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,12; 7,88</t>
+          <t>3,07; 6,92</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,91; 4,95</t>
+          <t>1,93; 5,23</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,79; 4,19</t>
+          <t>1,83; 4,59</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,53; 2,79</t>
+          <t>1,53; 2,8</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,45; 6,78</t>
+          <t>3,44; 6,69</t>
         </is>
       </c>
     </row>
@@ -1068,42 +1068,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>1,96</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>3,22</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1,8</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>6,82</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>2,1</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>2,06</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>3,61</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>2,59</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>1,96</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>3,22</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>1,8</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>6,73</t>
+          <t>2,57</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>4,75</t>
+          <t>4,74</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,38; 3,71</t>
+          <t>1,29; 3,7</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,33; 3,32</t>
+          <t>1,78; 6,12</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,0; 8,27</t>
+          <t>1,11; 3,16</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,03; 3,36</t>
+          <t>4,92; 12,28</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,25; 3,79</t>
+          <t>1,33; 3,67</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,9; 6,4</t>
+          <t>1,44; 3,64</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,19; 3,31</t>
+          <t>1,92; 8,38</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,69; 11,59</t>
+          <t>2,03; 3,32</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,49; 3,15</t>
+          <t>1,45; 3,14</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,85; 4,4</t>
+          <t>1,81; 4,22</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,76; 4,75</t>
+          <t>1,76; 5,36</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3,5; 7,86</t>
+          <t>3,66; 7,49</t>
         </is>
       </c>
     </row>
@@ -1208,42 +1208,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>2,72</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>2,43</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>1,89</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>5,12</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>2,77</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>2,58</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>2,84</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>3,84</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>2,72</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>2,43</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>1,89</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>5,01</t>
+          <t>3,81</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>4,5</t>
+          <t>4,54</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,03; 3,92</t>
+          <t>2,22; 3,68</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,03; 3,23</t>
+          <t>1,91; 3,3</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,26; 3,87</t>
+          <t>1,58; 2,31</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,25; 4,72</t>
+          <t>4,0; 6,87</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,14; 3,6</t>
+          <t>2,08; 4,2</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,94; 3,29</t>
+          <t>2,04; 3,24</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,62; 2,28</t>
+          <t>2,23; 3,78</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>3,97; 6,69</t>
+          <t>3,17; 4,72</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,27; 3,39</t>
+          <t>2,27; 3,44</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2,12; 3,0</t>
+          <t>2,13; 3,0</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2,04; 2,98</t>
+          <t>2,03; 2,9</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,88; 5,51</t>
+          <t>3,86; 5,59</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ14-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IQ14-Edad-trans_orig.xlsx
@@ -16,7 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +127,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +140,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N14"/>
+  <dimension ref="A1:N19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -646,419 +651,271 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>3,19</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>2,43</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>2,79</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>4,52</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>3,32</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>2,83</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>3,15</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>3,66</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>3,25</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>2,63</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>3,03</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>4,05</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>3.193339650146971</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>2.431593376703357</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>2.794335942393247</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>4.516300764788661</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>3.321189553681552</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>2.829574922690284</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>3.14890144490982</v>
+      </c>
+      <c r="J4" s="5" t="n">
+        <v>3.664981006017114</v>
+      </c>
+      <c r="K4" s="5" t="n">
+        <v>3.252419512384245</v>
+      </c>
+      <c r="L4" s="5" t="n">
+        <v>2.625762233289247</v>
+      </c>
+      <c r="M4" s="5" t="n">
+        <v>3.033037901393941</v>
+      </c>
+      <c r="N4" s="5" t="n">
+        <v>4.04962470443066</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>1,93; 5,06</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>1,71; 4,41</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>1,66; 4,99</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>1,48; 9,09</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>1,96; 5,34</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>1,87; 4,35</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>2,13; 4,67</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>2,15; 6,58</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>2,26; 4,54</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>1,97; 3,76</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>2,23; 4,22</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>2,43; 6,86</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>1.929162149015962</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>1.714370646240333</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>1.65948991020065</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>1.480831985201792</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>1.958981485467687</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>1.871933052827793</v>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>2.127577072287874</v>
+      </c>
+      <c r="J5" s="5" t="n">
+        <v>2.154491994671653</v>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>2.259829332471595</v>
+      </c>
+      <c r="L5" s="5" t="n">
+        <v>1.970760868657116</v>
+      </c>
+      <c r="M5" s="5" t="n">
+        <v>2.226068123515325</v>
+      </c>
+      <c r="N5" s="5" t="n">
+        <v>2.428659055954917</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>5.057095781671189</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>4.411121006756352</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>4.985748691482971</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>9.087919490124166</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>5.338303558845647</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>4.354303976954596</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>4.665221244215254</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>6.575087825392039</v>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>4.540405513856347</v>
+      </c>
+      <c r="L6" s="5" t="n">
+        <v>3.757251411617181</v>
+      </c>
+      <c r="M6" s="5" t="n">
+        <v>4.221144316976534</v>
+      </c>
+      <c r="N6" s="5" t="n">
+        <v>6.860987602308414</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>3-7</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>3,13</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>2,07</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>1,68</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>3,6</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>2,4</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>2,4</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>2,78</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>5,11</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>2,77</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>2,2</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>2,27</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>4,22</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>1,99; 5,72</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>1,53; 3,24</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>1,32; 2,32</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>2,48; 5,1</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>1,58; 5,94</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>1,52; 3,97</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>1,95; 4,88</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>3,66; 6,2</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>2,0; 4,14</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>1,7; 2,94</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>1,8; 3,41</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>3,35; 5,28</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>3.130067485490541</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>2.069385345818008</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>1.682561164696055</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>3.597414626733267</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>2.398863607270186</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>2.404648307162694</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>2.776674990053563</v>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>5.1126414380071</v>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>2.774802152854777</v>
+      </c>
+      <c r="L7" s="5" t="n">
+        <v>2.195826370545725</v>
+      </c>
+      <c r="M7" s="5" t="n">
+        <v>2.269042545651144</v>
+      </c>
+      <c r="N7" s="5" t="n">
+        <v>4.218554605383219</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>8-11</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>2,31</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>1,89</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>1,78</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>4,77</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>4,12</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>3,21</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>2,0</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>4,53</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>2,83</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>2,66</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>1,87</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>4,67</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>1.993534852213693</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>1.531634758722961</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>1.318897199364693</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>2.480914791883089</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>1.582860728471617</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>1.521313864730073</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>1.952308551138147</v>
+      </c>
+      <c r="J8" s="5" t="n">
+        <v>3.664260941816019</v>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>2.004484459095011</v>
+      </c>
+      <c r="L8" s="5" t="n">
+        <v>1.703984347728568</v>
+      </c>
+      <c r="M8" s="5" t="n">
+        <v>1.801458530408818</v>
+      </c>
+      <c r="N8" s="5" t="n">
+        <v>3.34897309488321</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>1,72; 3,13</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>1,15; 3,05</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>1,45; 2,07</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>3,21; 8,25</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>1,36; 11,47</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>2,01; 5,8</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>1,29; 4,02</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>3,07; 6,92</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>1,93; 5,23</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>1,83; 4,59</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>1,53; 2,8</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>3,44; 6,69</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>5.720251612884726</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>3.240308606703314</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>2.318276890669873</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>5.096413194909428</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>5.938952113801027</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>3.972582560053464</v>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>4.884453678652021</v>
+      </c>
+      <c r="J9" s="5" t="n">
+        <v>6.203454476699543</v>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>4.136417625107246</v>
+      </c>
+      <c r="L9" s="5" t="n">
+        <v>2.943037012565039</v>
+      </c>
+      <c r="M9" s="5" t="n">
+        <v>3.405997130227599</v>
+      </c>
+      <c r="N9" s="5" t="n">
+        <v>5.281903116537119</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>12-15</t>
+          <t>8-11</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -1066,277 +923,405 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>1,96</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>3,22</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1,8</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>6,82</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>2,1</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>2,06</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>3,61</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>2,57</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>2,04</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>2,7</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>2,68</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>4,74</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>2.306905898885913</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>1.889055504435139</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>1.778257676693179</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>4.769541398022126</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>4.123324577063065</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>3.205672507689546</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>1.995578765335967</v>
+      </c>
+      <c r="J10" s="5" t="n">
+        <v>4.532045689085465</v>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>2.831954157966508</v>
+      </c>
+      <c r="L10" s="5" t="n">
+        <v>2.656896693049848</v>
+      </c>
+      <c r="M10" s="5" t="n">
+        <v>1.873480596533119</v>
+      </c>
+      <c r="N10" s="5" t="n">
+        <v>4.67443588554436</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>1,29; 3,7</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>1,78; 6,12</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>1,11; 3,16</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>4,92; 12,28</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>1,33; 3,67</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>1,44; 3,64</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>1,92; 8,38</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>2,03; 3,32</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>1,45; 3,14</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>1,81; 4,22</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>1,76; 5,36</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>3,66; 7,49</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>1.715153044945028</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>1.147534207726315</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>1.451329181917104</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>3.213218957976417</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>1.356726171977219</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>2.011958817280942</v>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>1.287041088622738</v>
+      </c>
+      <c r="J11" s="5" t="n">
+        <v>3.066770372433783</v>
+      </c>
+      <c r="K11" s="5" t="n">
+        <v>1.93214965960364</v>
+      </c>
+      <c r="L11" s="5" t="n">
+        <v>1.83222585251984</v>
+      </c>
+      <c r="M11" s="5" t="n">
+        <v>1.531963307345278</v>
+      </c>
+      <c r="N11" s="5" t="n">
+        <v>3.439709275422744</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>3.131871211417278</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>3.048768091215779</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>2.069855539890093</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>8.251654790010571</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>11.465770032033</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>5.804192723519066</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>4.017195091310595</v>
+      </c>
+      <c r="J12" s="5" t="n">
+        <v>6.917692793695124</v>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>5.234197675061395</v>
+      </c>
+      <c r="L12" s="5" t="n">
+        <v>4.594653284259357</v>
+      </c>
+      <c r="M12" s="5" t="n">
+        <v>2.798309869073527</v>
+      </c>
+      <c r="N12" s="5" t="n">
+        <v>6.69233142301801</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>1.955786790201228</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>3.223214918343037</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>1.804751225611892</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>6.815379295286299</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>2.104315195186095</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>2.061527838928868</v>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>3.61456830082422</v>
+      </c>
+      <c r="J13" s="5" t="n">
+        <v>2.572542382014935</v>
+      </c>
+      <c r="K13" s="5" t="n">
+        <v>2.038066634741126</v>
+      </c>
+      <c r="L13" s="5" t="n">
+        <v>2.702928694295643</v>
+      </c>
+      <c r="M13" s="5" t="n">
+        <v>2.677605015897265</v>
+      </c>
+      <c r="N13" s="5" t="n">
+        <v>4.735548522809687</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>1.28684442381163</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>1.781990967446052</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>1.108175392844561</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>4.917363806406003</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>1.329820043943254</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>1.444661692751519</v>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>1.920426186500689</v>
+      </c>
+      <c r="J14" s="5" t="n">
+        <v>2.033285401384731</v>
+      </c>
+      <c r="K14" s="5" t="n">
+        <v>1.451101186090667</v>
+      </c>
+      <c r="L14" s="5" t="n">
+        <v>1.807338829288357</v>
+      </c>
+      <c r="M14" s="5" t="n">
+        <v>1.75647723130577</v>
+      </c>
+      <c r="N14" s="5" t="n">
+        <v>3.658697086614277</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>3.698306026786753</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>6.122072716899186</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>3.160662623354068</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>12.27584295066843</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>3.671345902841296</v>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>3.643533463662685</v>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v>8.376353273068501</v>
+      </c>
+      <c r="J15" s="5" t="n">
+        <v>3.321339191682843</v>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>3.137312669313408</v>
+      </c>
+      <c r="L15" s="5" t="n">
+        <v>4.216246003127346</v>
+      </c>
+      <c r="M15" s="5" t="n">
+        <v>5.360496681386558</v>
+      </c>
+      <c r="N15" s="5" t="n">
+        <v>7.492725060535744</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>2,72</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>2,43</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>1,89</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>5,12</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>2,77</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>2,58</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>2,84</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>3,81</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>2,74</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>2,5</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>2,39</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>4,54</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>2,22; 3,68</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>1,91; 3,3</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>1,58; 2,31</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>4,0; 6,87</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>2,08; 4,2</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>2,04; 3,24</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>2,23; 3,78</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>3,17; 4,72</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>2,27; 3,44</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>2,13; 3,0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>2,03; 2,9</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>3,86; 5,59</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>2.7157473084031</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>2.426476008722199</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>1.888457339479541</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>5.119087206083094</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>2.765330607319737</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>2.581378663833384</v>
+      </c>
+      <c r="I16" s="5" t="n">
+        <v>2.836747089976419</v>
+      </c>
+      <c r="J16" s="5" t="n">
+        <v>3.81203381734404</v>
+      </c>
+      <c r="K16" s="5" t="n">
+        <v>2.738368050166753</v>
+      </c>
+      <c r="L16" s="5" t="n">
+        <v>2.496365718461826</v>
+      </c>
+      <c r="M16" s="5" t="n">
+        <v>2.389753085717961</v>
+      </c>
+      <c r="N16" s="5" t="n">
+        <v>4.535792516445901</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>2.219361632368277</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>1.909241447837609</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>1.580688733570163</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>3.99926108856692</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>2.083811240031952</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>2.03676227362654</v>
+      </c>
+      <c r="I17" s="5" t="n">
+        <v>2.232357368784571</v>
+      </c>
+      <c r="J17" s="5" t="n">
+        <v>3.16509917571241</v>
+      </c>
+      <c r="K17" s="5" t="n">
+        <v>2.265020926931364</v>
+      </c>
+      <c r="L17" s="5" t="n">
+        <v>2.125380395995036</v>
+      </c>
+      <c r="M17" s="5" t="n">
+        <v>2.031956874367103</v>
+      </c>
+      <c r="N17" s="5" t="n">
+        <v>3.862592635105313</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>3.675658098589313</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>3.298807477853323</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>2.308832055243021</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>6.86776841469084</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>4.195253122394644</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>3.236412504667187</v>
+      </c>
+      <c r="I18" s="5" t="n">
+        <v>3.783151226843438</v>
+      </c>
+      <c r="J18" s="5" t="n">
+        <v>4.7216976878265</v>
+      </c>
+      <c r="K18" s="5" t="n">
+        <v>3.439103805410435</v>
+      </c>
+      <c r="L18" s="5" t="n">
+        <v>2.999988775499292</v>
+      </c>
+      <c r="M18" s="5" t="n">
+        <v>2.897774504835769</v>
+      </c>
+      <c r="N18" s="5" t="n">
+        <v>5.594812000573126</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1344,15 +1329,15 @@
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
     <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
